--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487981_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487981_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.346299999999999</v>
+        <v>8.492900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0289</v>
+        <v>5.0913</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3174</v>
+        <v>3.4016</v>
       </c>
       <c r="G2" t="n">
         <v>6.4684</v>
@@ -610,13 +610,13 @@
         <v>3.3698</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3293</v>
+        <v>-0.1826</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3816</v>
+        <v>-0.3192</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0524</v>
+        <v>0.1366</v>
       </c>
       <c r="V2" t="n">
         <v>1.8107</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.5104</v>
+        <v>6.9792</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7987</v>
+        <v>3.3517</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7117</v>
+        <v>3.6275</v>
       </c>
       <c r="G3" t="n">
         <v>4.1123</v>
@@ -688,13 +688,13 @@
         <v>3.7662</v>
       </c>
       <c r="S3" t="n">
-        <v>0.623</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1727</v>
+        <v>-0.2742</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4503</v>
+        <v>0.366</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.2911</v>
+        <v>4.4667</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4745</v>
+        <v>2.6782</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8166</v>
+        <v>1.7885</v>
       </c>
       <c r="G4" t="n">
         <v>1.707</v>
@@ -766,13 +766,13 @@
         <v>3.1716</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2683</v>
+        <v>-0.0926</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.756</v>
+        <v>-0.5523</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4877</v>
+        <v>0.4596</v>
       </c>
       <c r="V4" t="n">
         <v>0.8701</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2199</v>
+        <v>3.7107</v>
       </c>
       <c r="E5" t="n">
-        <v>0.441</v>
+        <v>0.7072000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>2.7789</v>
+        <v>3.0035</v>
       </c>
       <c r="G5" t="n">
         <v>-0.662</v>
@@ -844,13 +844,13 @@
         <v>3.3698</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7128</v>
+        <v>-0.222</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5688</v>
+        <v>-0.3027</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.144</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="V5" t="n">
         <v>2.4142</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. EGEA SOLER</t>
+          <t>B. GARCIA ALVAREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7436</v>
+        <v>2.4948</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4015</v>
+        <v>0.5232</v>
       </c>
       <c r="F6" t="n">
-        <v>3.145</v>
+        <v>1.9715</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.8216</v>
+        <v>1.4994</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.5227</v>
+        <v>0.998</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.2989</v>
+        <v>0.5013</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.053</v>
+        <v>2.202</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.8671</v>
+        <v>1.5877</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.1859</v>
+        <v>0.6143</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7685999999999999</v>
+        <v>-0.7027</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6556</v>
+        <v>-0.5896</v>
       </c>
       <c r="O6" t="n">
         <v>-0.113</v>
       </c>
       <c r="P6" t="n">
-        <v>3.568</v>
+        <v>2.5769</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.3876</v>
       </c>
       <c r="R6" t="n">
-        <v>3.568</v>
+        <v>3.9645</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3936</v>
+        <v>-0.3744</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0479</v>
+        <v>-0.5578</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3456</v>
+        <v>0.1834</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6036</v>
+        <v>-1.2071</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6036</v>
+        <v>0.2666</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. GARCIA ALVAREZ</t>
+          <t>E. EGEA SOLER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3803</v>
+        <v>1.6189</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4789</v>
+        <v>-1.5823</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8592</v>
+        <v>3.2012</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4994</v>
+        <v>-2.8216</v>
       </c>
       <c r="H7" t="n">
-        <v>0.998</v>
+        <v>-1.5227</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5013</v>
+        <v>-1.2989</v>
       </c>
       <c r="J7" t="n">
-        <v>2.202</v>
+        <v>-2.053</v>
       </c>
       <c r="K7" t="n">
-        <v>1.5877</v>
+        <v>-0.8671</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6143</v>
+        <v>-1.1859</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7027</v>
+        <v>-0.7685999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5896</v>
+        <v>-0.6556</v>
       </c>
       <c r="O7" t="n">
         <v>-0.113</v>
       </c>
       <c r="P7" t="n">
-        <v>2.5769</v>
+        <v>3.568</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.3876</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.9645</v>
+        <v>3.568</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.4888</v>
+        <v>0.2689</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.5599</v>
+        <v>-0.1329</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0711</v>
+        <v>0.4018</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2071</v>
+        <v>0.6036</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2666</v>
+        <v>0.6036</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.4737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0469</v>
+        <v>1.0364</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1982</v>
+        <v>-0.0964</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2451</v>
+        <v>1.1328</v>
       </c>
       <c r="G8" t="n">
         <v>0.2717</v>
@@ -1078,13 +1078,13 @@
         <v>0.1982</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1013</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.1019</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1013</v>
+        <v>-0.011</v>
       </c>
       <c r="V8" t="n">
         <v>0.674</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0045</v>
+        <v>0.1969</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5323</v>
+        <v>-0.368</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.5649</v>
       </c>
       <c r="G9" t="n">
         <v>-0.0142</v>
@@ -1156,13 +1156,13 @@
         <v>0.3964</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1795</v>
+        <v>0.0128</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3744</v>
+        <v>-0.2101</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1949</v>
+        <v>0.223</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. SANCHES CARDOSO MENDES</t>
+          <t>A. ARTILES AGUILAR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1805</v>
+        <v>-1.1231</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3566</v>
+        <v>-0.1872</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1761</v>
+        <v>-0.9359</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-1.2573</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.6767</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.2551</v>
+        <v>-1.934</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4979</v>
+        <v>0.6643</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1009</v>
+        <v>1.0025</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5988</v>
+        <v>-0.3383</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.175</v>
+        <v>-1.9215</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4813</v>
+        <v>-0.3258</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6563</v>
+        <v>-1.5957</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9911</v>
+        <v>1.784</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1805</v>
+        <v>-0.1982</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1893</v>
+        <v>1.9822</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2169</v>
+        <v>-0.1762</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0552</v>
+        <v>-0.6533</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1618</v>
+        <v>0.4771</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2666</v>
+        <v>-1.4737</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. ARTILES AGUILAR</t>
+          <t>R. SANCHES CARDOSO MENDES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6554</v>
+        <v>-1.2938</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7195</v>
+        <v>-2.498</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9359</v>
+        <v>1.2042</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.2573</v>
+        <v>-0.6729000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6767</v>
+        <v>0.5822000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.934</v>
+        <v>-1.2551</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6643</v>
+        <v>-0.4979</v>
       </c>
       <c r="K11" t="n">
-        <v>1.0025</v>
+        <v>0.1009</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.3383</v>
+        <v>-0.5988</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.9215</v>
+        <v>-0.175</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3258</v>
+        <v>0.4813</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.5957</v>
+        <v>-0.6563</v>
       </c>
       <c r="P11" t="n">
-        <v>1.784</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.1982</v>
+        <v>-2.1805</v>
       </c>
       <c r="R11" t="n">
-        <v>1.9822</v>
+        <v>1.1893</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7084</v>
+        <v>0.1037</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1855</v>
+        <v>-0.0862</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4771</v>
+        <v>0.1899</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.4737</v>
+        <v>0.2666</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.4737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.7525</v>
+        <v>-2.6891</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.1399</v>
+        <v>-4.7677</v>
       </c>
       <c r="F12" t="n">
-        <v>2.3874</v>
+        <v>2.0786</v>
       </c>
       <c r="G12" t="n">
         <v>-6.0195</v>
@@ -1390,13 +1390,13 @@
         <v>2.7751</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5267</v>
+        <v>0.5901</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4775</v>
+        <v>-0.1503</v>
       </c>
       <c r="U12" t="n">
-        <v>1.0493</v>
+        <v>0.7403999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>2.3438</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>22.9546</v>
+        <v>23.8905</v>
       </c>
       <c r="E13" t="n">
-        <v>1.916200000000001</v>
+        <v>2.852000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>21.0383</v>
+        <v>21.0384</v>
       </c>
       <c r="G13" t="n">
         <v>2.611299999999999</v>
@@ -1456,7 +1456,7 @@
         <v>-3.5684</v>
       </c>
       <c r="O13" t="n">
-        <v>-4.5258</v>
+        <v>-4.525799999999999</v>
       </c>
       <c r="P13" t="n">
         <v>14.8666</v>
@@ -1468,16 +1468,16 @@
         <v>27.7511</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8256000000000001</v>
+        <v>0.1103</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.0729</v>
+        <v>-3.1371</v>
       </c>
       <c r="U13" t="n">
         <v>3.2475</v>
       </c>
       <c r="V13" t="n">
-        <v>6.3022</v>
+        <v>6.302199999999999</v>
       </c>
       <c r="W13" t="n">
         <v>8.168200000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.8333</v>
+        <v>6.1457</v>
       </c>
       <c r="E14" t="n">
-        <v>5.9925</v>
+        <v>6.3999</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8408</v>
+        <v>-0.2542</v>
       </c>
       <c r="G14" t="n">
         <v>6.5229</v>
@@ -1546,13 +1546,13 @@
         <v>2.1805</v>
       </c>
       <c r="S14" t="n">
-        <v>0.793</v>
+        <v>0.1054</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.4975</v>
+        <v>-1.0901</v>
       </c>
       <c r="U14" t="n">
-        <v>2.2905</v>
+        <v>1.1955</v>
       </c>
       <c r="V14" t="n">
         <v>-1.4737</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. TERRÓN FERNÁNDEZ</t>
+          <t>J. LUQUE GOMEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6027</v>
+        <v>0.9641999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6027</v>
+        <v>-0.1211</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1.0853</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6027</v>
+        <v>0.6694</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>-2.2003</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6027</v>
+        <v>2.8697</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6027</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>-1.0014</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6027</v>
+        <v>1.8961</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>-0.2253</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>-1.1989</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>0.9736</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.5858</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.1982</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.784</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-0.6874</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>-0.8175</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>0.1301</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. LUQUE GOMEZ</t>
+          <t>D. TERRÓN FERNÁNDEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3778</v>
+        <v>0.6027</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4267</v>
+        <v>0.6027</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8045</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6694</v>
+        <v>0.6027</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.2003</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8697</v>
+        <v>0.6027</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8947000000000001</v>
+        <v>0.6027</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.0014</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1.8961</v>
+        <v>0.6027</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2253</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1989</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9736</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5858</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1982</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.784</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2738</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1232</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1506</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3742</v>
+        <v>0.4761</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0222</v>
+        <v>0.0796</v>
       </c>
       <c r="F17" t="n">
         <v>0.3964</v>
@@ -1780,10 +1780,10 @@
         <v>0.3964</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1982</v>
+        <v>-0.0964</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0624</v>
+        <v>0.0395</v>
       </c>
       <c r="U17" t="n">
         <v>-0.1358</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7019</v>
+        <v>-0.4806</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.5868</v>
+        <v>-1.2812</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8848</v>
+        <v>0.8006</v>
       </c>
       <c r="G18" t="n">
         <v>-0.5503</v>
@@ -1858,13 +1858,13 @@
         <v>0.5947</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2448</v>
+        <v>0.4662</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.624</v>
+        <v>-0.3184</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8688</v>
+        <v>0.7845</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. CORTES ANDRADES</t>
+          <t>N. ESCOLANO ZAVALA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4163</v>
+        <v>-1.8409</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0349</v>
+        <v>-0.6896</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6186</v>
+        <v>-1.1513</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.0219</v>
+        <v>-1.7715</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3248</v>
+        <v>0.3159</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.6971</v>
+        <v>-2.0874</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.5887</v>
+        <v>0.4841</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.2706</v>
+        <v>0.4439</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.3181</v>
+        <v>0.0402</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4331</v>
+        <v>-2.2556</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0542</v>
+        <v>-0.128</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.379</v>
+        <v>-2.1276</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.5947</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.3876</v>
+        <v>-1.1893</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7929</v>
+        <v>0.3964</v>
       </c>
       <c r="S19" t="n">
-        <v>1.5263</v>
+        <v>0.0496</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7343</v>
+        <v>0.0157</v>
       </c>
       <c r="U19" t="n">
-        <v>0.792</v>
+        <v>0.0339</v>
       </c>
       <c r="V19" t="n">
         <v>0.674</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5331</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.721</v>
+        <v>-1.8862</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1454</v>
+        <v>-1.4511</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5755</v>
+        <v>-0.4351</v>
       </c>
       <c r="G20" t="n">
         <v>-1.4461</v>
@@ -2014,13 +2014,13 @@
         <v>0.3964</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2515</v>
+        <v>0.0863</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4295</v>
+        <v>0.1239</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1781</v>
+        <v>-0.0377</v>
       </c>
       <c r="V20" t="n">
         <v>0.2666</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>N. ESCOLANO ZAVALA</t>
+          <t>D. CORTES ANDRADES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0479</v>
+        <v>-1.9818</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5877</v>
+        <v>-2.5442</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4602</v>
+        <v>0.5624</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.7715</v>
+        <v>-3.0219</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3159</v>
+        <v>-1.3248</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.0874</v>
+        <v>-1.6971</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4841</v>
+        <v>-2.5887</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4439</v>
+        <v>-1.2706</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0402</v>
+        <v>-1.3181</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.2556</v>
+        <v>-0.4331</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.128</v>
+        <v>-0.0542</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.1276</v>
+        <v>-0.379</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.7929</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1893</v>
+        <v>-1.3876</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3964</v>
+        <v>0.7929</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1574</v>
+        <v>0.9608</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1176</v>
+        <v>0.2249</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.275</v>
+        <v>0.7358</v>
       </c>
       <c r="V21" t="n">
         <v>0.674</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X21" t="n">
-        <v>0.674</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>T. WOLKOWYSKI</t>
+          <t>R. VIDALES MOLINA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9584</v>
+        <v>-4.3143</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.036</v>
+        <v>-6.2862</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0776</v>
+        <v>1.9719</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2701</v>
+        <v>0.1522</v>
       </c>
       <c r="H22" t="n">
-        <v>0.07439999999999999</v>
+        <v>0.3111</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3445</v>
+        <v>-0.1589</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2425</v>
+        <v>0.2399</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2023</v>
+        <v>0.8348</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0402</v>
+        <v>-0.5949</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5125999999999999</v>
+        <v>-0.0877</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.128</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3847</v>
+        <v>0.436</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.7662</v>
+        <v>-4.1627</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.9556</v>
+        <v>-6.3431</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1893</v>
+        <v>2.1805</v>
       </c>
       <c r="S22" t="n">
-        <v>2.2851</v>
+        <v>-0.3038</v>
       </c>
       <c r="T22" t="n">
-        <v>1.351</v>
+        <v>-0.4495</v>
       </c>
       <c r="U22" t="n">
-        <v>0.9341</v>
+        <v>0.1457</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.674</v>
+        <v>0.2666</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5331</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. TERRON FERNANDEZ</t>
+          <t>T. WOLKOWYSKI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.0291</v>
+        <v>-4.3983</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8688</v>
+        <v>-5.0547</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.1603</v>
+        <v>0.6564</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.6541</v>
+        <v>-0.2701</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.378</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.2761</v>
+        <v>-0.3445</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.2626</v>
+        <v>0.2425</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8947000000000001</v>
+        <v>0.2023</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.1574</v>
+        <v>0.0402</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3914</v>
+        <v>-0.5125999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.2727</v>
+        <v>-0.128</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1187</v>
+        <v>-0.3847</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.3876</v>
+        <v>-3.7662</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9822</v>
+        <v>-4.9556</v>
       </c>
       <c r="R23" t="n">
-        <v>0.5947</v>
+        <v>1.1893</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7804</v>
+        <v>0.8452</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.624</v>
+        <v>0.3323</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1564</v>
+        <v>0.5129</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2071</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-0.674</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2071</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R. VIDALES MOLINA</t>
+          <t>D. TERRON FERNANDEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.1782</v>
+        <v>-4.7131</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.8975</v>
+        <v>-2.6651</v>
       </c>
       <c r="F24" t="n">
-        <v>1.7192</v>
+        <v>-2.048</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1522</v>
+        <v>-1.6541</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3111</v>
+        <v>-0.378</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1589</v>
+        <v>-1.2761</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2399</v>
+        <v>-0.2626</v>
       </c>
       <c r="K24" t="n">
-        <v>0.8348</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5949</v>
+        <v>-1.1574</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.0877</v>
+        <v>-1.3914</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.5237000000000001</v>
+        <v>-1.2727</v>
       </c>
       <c r="O24" t="n">
-        <v>0.436</v>
+        <v>-0.1187</v>
       </c>
       <c r="P24" t="n">
-        <v>-4.1627</v>
+        <v>-1.3876</v>
       </c>
       <c r="Q24" t="n">
-        <v>-6.3431</v>
+        <v>-1.9822</v>
       </c>
       <c r="R24" t="n">
-        <v>2.1805</v>
+        <v>0.5947</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1677</v>
+        <v>-0.4644</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0608</v>
+        <v>-0.4202</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.107</v>
+        <v>-0.0441</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.2666</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A. MAYOR MARTIN</t>
+          <t>E. LOPEZ GARCIA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.8784</v>
+        <v>-5.6145</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.8576</v>
+        <v>-3.9661</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.0208</v>
+        <v>-1.6484</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-2.012</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.0492</v>
+        <v>-1.6024</v>
       </c>
       <c r="I25" t="n">
-        <v>1.0407</v>
+        <v>-0.4096</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6243</v>
+        <v>0.969</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0138</v>
+        <v>0.2018</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6104000000000001</v>
+        <v>0.7673</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.6328</v>
+        <v>-2.981</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.0631</v>
+        <v>-1.8042</v>
       </c>
       <c r="O25" t="n">
-        <v>0.4303</v>
+        <v>-1.1768</v>
       </c>
       <c r="P25" t="n">
-        <v>-3.3698</v>
+        <v>-2.5769</v>
       </c>
       <c r="Q25" t="n">
         <v>-4.1627</v>
       </c>
       <c r="R25" t="n">
-        <v>0.7929</v>
+        <v>1.5858</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0859</v>
+        <v>-0.0147</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3192</v>
+        <v>-0.3651</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2333</v>
+        <v>0.3504</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.4142</v>
+        <v>-1.0109</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>-0.4074</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.4142</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>E. LOPEZ GARCIA</t>
+          <t>A. MAYOR MARTIN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.2113</v>
+        <v>-5.9137</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.1698</v>
+        <v>-4.0614</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.0415</v>
+        <v>-1.8523</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.012</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.6024</v>
+        <v>-1.0492</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4096</v>
+        <v>1.0407</v>
       </c>
       <c r="J26" t="n">
-        <v>0.969</v>
+        <v>0.6243</v>
       </c>
       <c r="K26" t="n">
-        <v>0.2018</v>
+        <v>0.0138</v>
       </c>
       <c r="L26" t="n">
-        <v>0.7673</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.981</v>
+        <v>-0.6328</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.8042</v>
+        <v>-1.0631</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.1768</v>
+        <v>0.4303</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.5769</v>
+        <v>-3.3698</v>
       </c>
       <c r="Q26" t="n">
         <v>-4.1627</v>
       </c>
       <c r="R26" t="n">
-        <v>1.5858</v>
+        <v>0.7929</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.6115</v>
+        <v>-0.1212</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5688</v>
+        <v>-0.523</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.0427</v>
+        <v>0.4018</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.0109</v>
+        <v>-2.4142</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.4074</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.6036</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-22.9545</v>
+        <v>-22.9547</v>
       </c>
       <c r="E27" t="n">
-        <v>-21.0382</v>
+        <v>-21.0385</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.9164</v>
+        <v>-1.9163</v>
       </c>
       <c r="G27" t="n">
         <v>-2.6113</v>
@@ -2530,13 +2530,13 @@
         <v>-4.055099999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>1.443699999999999</v>
+        <v>1.4437</v>
       </c>
       <c r="J27" t="n">
-        <v>8.0944</v>
+        <v>8.094399999999998</v>
       </c>
       <c r="K27" t="n">
-        <v>3.568499999999999</v>
+        <v>3.5685</v>
       </c>
       <c r="L27" t="n">
         <v>4.5259</v>
@@ -2560,13 +2560,13 @@
         <v>12.8845</v>
       </c>
       <c r="S27" t="n">
-        <v>0.8258</v>
+        <v>0.8255999999999998</v>
       </c>
       <c r="T27" t="n">
         <v>-3.2475</v>
       </c>
       <c r="U27" t="n">
-        <v>4.0731</v>
+        <v>4.073000000000001</v>
       </c>
       <c r="V27" t="n">
         <v>-6.302</v>
